--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -492,16 +492,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>たいてい</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>大抵，大都</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -510,38 +510,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>により</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>携带；随身携带</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>もちあるく</t>
-        </is>
-      </c>
+          <t>根据，由于</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>立ち寄る</t>
+          <t>および</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>顺路去；顺便到</t>
+          <t>以及，和</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -550,7 +546,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -572,25 +568,29 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>ほしがる</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>（第三方）想要</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>たがる-&gt;第三人称想要</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -634,34 +634,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ほうっておく</t>
+          <t>直後</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>置之不理，放任不管</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>之后不久，紧接着</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ちょくご</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>だいぶ</t>
+          <t>なぐさめる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>相当；颇；很；很多</t>
+          <t>安慰，慰问</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -670,38 +674,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>真剣さ</t>
+          <t>いっこう〜ない</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>认真，严肃（的程度）</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>しんけんさ</t>
-        </is>
-      </c>
+          <t>一点也（不）......</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>まったく-&gt;完全地</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>それだけ</t>
+          <t>それぞれ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>只有那么些，仅此而已</t>
+          <t>各自，分别</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -714,37 +718,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>〜方がいい</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>弄丢，失去</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>最好…</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>〜ほうがいい</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>とれる</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>それぞれ</t>
+          <t>生産的</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>各自，分别</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>有生产性的，有成果的</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>せいさんてき</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
     </row>
@@ -754,30 +762,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>必ずしも〜ない</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
+          <t>弄丢，失去</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>とれる</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>たいてい</t>
+          <t>必ずしも〜ない</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大抵，大都</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -786,38 +798,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>いっこう〜ない</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>一点也（不）......</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>まったく-&gt;完全地</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>なぐさめる</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>安慰，慰问</t>
+          <t>只有那么些，仅此而已</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -830,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>生産的</t>
+          <t>真剣さ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>有生产性的，有成果的</t>
+          <t>认真，严肃（的程度）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>せいさんてき</t>
+          <t>しんけんさ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -848,82 +856,70 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>直後</t>
+          <t>だいぶ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>之后不久，紧接着</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ちょくご</t>
-        </is>
-      </c>
+          <t>相当；颇；很；很多</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜方がいい</t>
+          <t>ほうっておく</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>最好…</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>〜ほうがいい</t>
-        </is>
-      </c>
+          <t>置之不理，放任不管</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ほしがる</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>（第三方）想要</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>たがる-&gt;第三人称想要</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>および</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>以及，和</t>
+          <t>顺路去；顺便到</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -936,21 +932,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>により</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>根据，由于</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>携带；随身携带</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>もちあるく</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -470,43 +470,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>かなり</t>
+          <t>により</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>相当，很</t>
+          <t>根据，由于</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;除…之外</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>たいてい</t>
+          <t>ふりがな</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大抵，大都</t>
+          <t>变更</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>振替</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -514,79 +514,87 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>により</t>
+          <t>ほしがる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>根据，由于</t>
+          <t>（第三方）想要</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>たがる-&gt;第三人称想要</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>および</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>以及，和</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ふりがな</t>
+          <t>押し寄せちる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>蜂拥而至，涌上来</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>おしよせる</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>振替</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ほしがる</t>
+          <t>直後</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>（第三方）想要</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>之后不久，紧接着</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ちょくご</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>たがる-&gt;第三人称想要</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -594,78 +602,74 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>なぐさめる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>安慰，慰问</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>押し寄せちる</t>
+          <t>いっこう〜ない</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>蜂拥而至，涌上来</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>おしよせる</t>
-        </is>
-      </c>
+          <t>一点也（不）......</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>まったく-&gt;完全地</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>直後</t>
+          <t>かなり</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>之后不久，紧接着</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ちょくご</t>
-        </is>
-      </c>
+          <t>相当，很</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;除…之外</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>なぐさめる</t>
+          <t>たいてい</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>安慰，慰问</t>
+          <t>大抵，大都</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -678,34 +682,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>いっこう〜ない</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>一点也（不）......</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>携带；随身携带</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>もちあるく</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>まったく-&gt;完全地</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>それぞれ</t>
+          <t>ほうっておく</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>各自，分别</t>
+          <t>置之不理，放任不管</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -714,21 +718,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜方がいい</t>
+          <t>持ち運び</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>最好…</t>
+          <t>搬运；携带</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>〜ほうがいい</t>
+          <t>もちはこび</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -736,47 +740,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>生産的</t>
+          <t>それぞれ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>有生产性的，有成果的</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>せいさんてき</t>
-        </is>
-      </c>
+          <t>各自，分别</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>および</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>弄丢，失去</t>
+          <t>以及，和</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>とれる</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -784,15 +780,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>必ずしも〜ない</t>
+          <t>生産的</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>有生产性的，有成果的</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>せいさんてき</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
     </row>
@@ -802,17 +802,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>弄丢，失去</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>とれる</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -820,12 +824,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>それだけ</t>
+          <t>必ずしも〜ない</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>只有那么些，仅此而已</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -838,19 +842,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>真剣さ</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>认真，严肃（的程度）</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>しんけんさ</t>
-        </is>
-      </c>
+          <t>尽可能地，尽量</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>だいぶ</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>相当；颇；很；很多</t>
+          <t>只有那么些，仅此而已</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -874,19 +874,23 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ほうっておく</t>
+          <t>真剣さ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>置之不理，放任不管</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>认真，严肃（的程度）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>しんけんさ</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
     </row>
@@ -896,12 +900,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>だいぶ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>相当；颇；很；很多</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -914,12 +918,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>立ち寄る</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>顺路去；顺便到</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -928,43 +932,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>携带；随身携带</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>もちあるく</t>
-        </is>
-      </c>
+          <t>顺路去；顺便到</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>持ち運び</t>
+          <t>〜方がいい</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>搬运；携带</t>
+          <t>最好…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>もちはこび</t>
+          <t>〜ほうがいい</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -465,28 +465,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ふりがな</t>
+          <t>直後</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>振替</t>
-        </is>
-      </c>
+          <t>之后不久，紧接着</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ちょくご</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -507,24 +507,24 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>直後</t>
+          <t>ふりがな</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>之后不久，紧接着</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ちょくご</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>变更</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>振替</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -549,16 +549,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>により</t>
+          <t>ほうっておく</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>根据，由于</t>
+          <t>置之不理，放任不管</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ほうっておく</t>
+          <t>により</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>置之不理，放任不管</t>
+          <t>根据，由于</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -583,61 +583,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>なぐさめる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>携带；随身携带</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>もちあるく</t>
-        </is>
-      </c>
+          <t>安慰，慰问</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>持ち運び</t>
+          <t>ほしがる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>搬运；携带</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>もちはこび</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>（第三方）想要</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>たがる-&gt;第三人称想要</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>なぐさめる</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>安慰，慰问</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>携带；随身携带</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>もちあるく</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -646,20 +646,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>持ち運び</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
-        </is>
-      </c>
+          <t>搬运；携带</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>もちはこび</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,18 +667,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ほしがる</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>（第三方）想要</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>たがる-&gt;第三人称想要</t>
+          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>たいてい</t>
+          <t>だいぶ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>大抵，大都</t>
+          <t>相当；颇；很；很多</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -722,16 +722,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>それぞれ</t>
+          <t>かなり</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>各自，分别</t>
+          <t>相当，很</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;除…之外</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -739,40 +743,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>かなり</t>
+          <t>たいてい</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>相当，很</t>
+          <t>大抵，大都</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;除…之外</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>真剣さ</t>
+          <t>それぞれ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>认真，严肃（的程度）</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>しんけんさ</t>
-        </is>
-      </c>
+          <t>各自，分别</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -781,15 +777,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>立ち寄る</t>
+          <t>真剣さ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>顺路去；顺便到</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>认真，严肃（的程度）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>しんけんさ</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -798,12 +798,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>顺路去；顺便到</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -815,12 +815,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>だいぶ</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>相当；颇；很；很多</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE9C911-E437-4A5A-B1B8-FD74B62BCF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D95A1F-991A-4406-AB98-5F6FDDA9CA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10560" yWindow="885" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>Fre</t>
   </si>
@@ -219,20 +219,157 @@
     <t>顺路去；顺便到</t>
   </si>
   <si>
+    <t>最好…</t>
+  </si>
+  <si>
+    <t>〜ほうがいい</t>
+  </si>
+  <si>
+    <t>あまり～ない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ならば</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果…的话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>採用の面接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>录用面试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于；通过；根据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜により</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地点，目的地；前面；尖端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>えさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饲料；诱饵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あまりほしがらなくなります</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变得不怎么想要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>で</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并且</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ておけば</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>款式，模型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>だけでなく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不仅仅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>すべて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部，所有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>これほど～ないだろう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有比这更…的吧(最高级)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もしかしたら</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许，说不定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>順番</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふつう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通，通常，平常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ただ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅仅；免费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>〜方がいい</t>
-  </si>
-  <si>
-    <t>最好…</t>
-  </si>
-  <si>
-    <t>〜ほうがいい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"ておく"提前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,17 +378,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -289,11 +436,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -596,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="25.875" customWidth="1"/>
@@ -623,321 +771,579 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="A13" s="2">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>1</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>0</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>0</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E18" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>0</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>0</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>0</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>0</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>0</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>0</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>0</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>0</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="C27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>2</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>2</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>2</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>2</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>2</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>2</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>2</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -948,7 +1354,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -958,7 +1364,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.875" customWidth="1" min="2" max="2"/>
@@ -465,36 +465,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>により</t>
+          <t>直後</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>根据，由于</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>之后不久，紧接着</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ちょくご</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ふつう</t>
+          <t>押し寄せちる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>普通，通常，平常</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>蜂拥而至，涌上来</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>おしよせる</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -503,20 +511,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>直後</t>
+          <t>ふりがな</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>之后不久，紧接着</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ちょくご</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>变更</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>振替</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,16 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ほうっておく</t>
+          <t>いっこう〜ない</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>置之不理，放任不管</t>
+          <t>一点也（不）......</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>まったく-&gt;完全地</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,12 +553,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>ほうっておく</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>饲料；诱饵</t>
+          <t>置之不理，放任不管</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -554,16 +566,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>これほど～ないだろう</t>
+          <t>により</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>没有比这更…的吧(最高级)</t>
+          <t>根据，由于</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -571,16 +583,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>モデル</t>
+          <t>なぐさめる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>款式，模型</t>
+          <t>安慰，慰问</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -588,92 +600,100 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>もしかしたら</t>
+          <t>ほしがる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>或许，说不定</t>
+          <t>（第三方）想要</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>たがる-&gt;第三人称想要</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ただ</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>仅仅；免费</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>携带；随身携带</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>もちあるく</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ふりがな</t>
+          <t>持ち運び</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>振替</t>
-        </is>
-      </c>
+          <t>搬运；携带</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>もちはこび</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>いっこう〜ない</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>一点也（不）......</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>まったく-&gt;完全地</t>
+          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>なぐさめる</t>
+          <t>および</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>安慰，慰问</t>
+          <t>以及，和</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -681,16 +701,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>先</t>
+          <t>だいぶ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>地点，目的地；前面；尖端</t>
+          <t>相当；颇；很；很多</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -698,37 +718,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>かなり</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>携带；随身携带</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>もちあるく</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>相当，很</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;除…之外</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>あまりほしがらなくなります</t>
+          <t>たいてい</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>变得不怎么想要</t>
+          <t>大抵，大都</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -736,113 +756,109 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>押し寄せちる</t>
+          <t>それぞれ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>蜂拥而至，涌上来</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>おしよせる</t>
-        </is>
-      </c>
+          <t>各自，分别</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ておけば</t>
+          <t>真剣さ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>"ておく"提前</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>认真，严肃（的程度）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>しんけんさ</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>持ち運び</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>搬运；携带</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>もちはこび</t>
-        </is>
-      </c>
+          <t>顺路去；顺便到</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ほしがる</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>（第三方）想要</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>たがる-&gt;第三人称想要</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>で</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>并且</t>
+          <t>弄丢，失去</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>とれる</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>だけでなく</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>不仅仅</t>
+          <t>只有那么些，仅此而已</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -850,37 +866,33 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>採用の面接</t>
+          <t>必ずしも〜ない</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>录用面试</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -888,346 +900,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>あまり～ない</t>
+          <t>生産的</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>不太…</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>有生产性的，有成果的</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>せいさんてき</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>〜方がいい</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>由于；通过；根据</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>最好…</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>〜ほうがいい</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ならば</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>如果…的话</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>順番</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>顺序</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>すべて</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>全部，所有</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>たいてい</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>大抵，大都</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>および</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>以及，和</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>かなり</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>相当，很</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;除…之外</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>それぞれ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>各自，分别</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>0</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>必ずしも〜ない</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>0</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>立ち寄る</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>顺路去；顺便到</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>生産的</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>有生产性的，有成果的</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>せいさんてき</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>0</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>なくす</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>弄丢，失去</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>とれる</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>0</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>できるだけ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>尽可能地，尽量</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>すでに</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>0</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>それだけ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>只有那么些，仅此而已</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>真剣さ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>认真，严肃（的程度）</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>しんけんさ</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>0</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>〜方がいい</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>最好…</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>〜ほうがいい</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>だいぶ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>相当；颇；很；很多</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -465,16 +465,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>により</t>
+          <t>ほうっておく</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>根据，由于</t>
+          <t>置之不理，放任不管</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -482,16 +482,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ふつう</t>
+          <t>これほど～ないだろう</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>普通，通常，平常</t>
+          <t>没有比这更…的吧(最高级)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -520,16 +520,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ほうっておく</t>
+          <t>あまりほしがらなくなります</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>置之不理，放任不管</t>
+          <t>变得不怎么想要</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -537,16 +537,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>により</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>饲料；诱饵</t>
+          <t>根据，由于</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -554,33 +554,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>これほど～ないだろう</t>
+          <t>押し寄せちる</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>没有比这更…的吧(最高级)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>蜂拥而至，涌上来</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>おしよせる</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>モデル</t>
+          <t>ておけば</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>款式，模型</t>
+          <t>"ておく"提前</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -592,12 +596,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>もしかしたら</t>
+          <t>えさ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>或许，说不定</t>
+          <t>饲料；诱饵</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -605,7 +609,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -622,58 +626,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ふりがな</t>
+          <t>ふつう</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>变更</t>
+          <t>普通，通常，平常</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>振替</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>いっこう〜ない</t>
+          <t>もしかしたら</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>一点也（不）......</t>
+          <t>或许，说不定</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>まったく-&gt;完全地</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>なぐさめる</t>
+          <t>モデル</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>安慰，慰问</t>
+          <t>款式，模型</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -685,36 +681,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>先</t>
+          <t>いっこう〜ない</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>地点，目的地；前面；尖端</t>
+          <t>一点也（不）......</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>まったく-&gt;完全地</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>先</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>携带；随身携带</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>もちあるく</t>
-        </is>
-      </c>
+          <t>地点，目的地；前面；尖端</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -723,16 +719,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>あまりほしがらなくなります</t>
+          <t>ふりがな</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>变得不怎么想要</t>
+          <t>变更</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>振替</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>押し寄せちる</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>蜂拥而至，涌上来</t>
+          <t>携带；随身携带</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>おしよせる</t>
+          <t>もちあるく</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ておけば</t>
+          <t>なぐさめる</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>"ておく"提前</t>
+          <t>安慰，慰问</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -774,23 +774,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>持ち運び</t>
+          <t>採用の面接</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>搬运；携带</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>もちはこび</t>
-        </is>
-      </c>
+          <t>录用面试</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -820,12 +816,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>で</t>
+          <t>ならば</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>并且</t>
+          <t>如果…的话</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -837,16 +833,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>だけでなく</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>不仅仅</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -854,20 +854,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>たいてい</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>大抵，大都</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -875,12 +871,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>採用の面接</t>
+          <t>だけでなく</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>录用面试</t>
+          <t>不仅仅</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -892,12 +888,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>あまり～ない</t>
+          <t>で</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>不太…</t>
+          <t>并且</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -909,15 +905,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>持ち運び</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>由于；通过；根据</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>搬运；携带</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>もちはこび</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -926,12 +926,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ならば</t>
+          <t>順番</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>如果…的话</t>
+          <t>顺序</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -943,12 +943,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>順番</t>
+          <t>〜により</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>顺序</t>
+          <t>由于；通过；根据</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -977,12 +977,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>たいてい</t>
+          <t>あまり～ない</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>大抵，大都</t>
+          <t>不太…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -994,12 +994,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>および</t>
+          <t>だいぶ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>以及，和</t>
+          <t>相当；颇；很；很多</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1011,20 +1011,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>かなり</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>相当，很</t>
+          <t>顺路去；顺便到</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;除…之外</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1032,12 +1028,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>それぞれ</t>
+          <t>および</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>各自，分别</t>
+          <t>以及，和</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1045,33 +1041,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>必ずしも〜ない</t>
+          <t>かなり</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
+          <t>相当，很</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;除…之外</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>立ち寄る</t>
+          <t>それぞれ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>顺路去；顺便到</t>
+          <t>各自，分别</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1083,19 +1083,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>生産的</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>有生产性的，有成果的</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>せいさんてき</t>
-        </is>
-      </c>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1104,20 +1100,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>真剣さ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>弄丢，失去</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>とれる</t>
-        </is>
-      </c>
+          <t>认真，严肃（的程度）</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>しんけんさ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1125,12 +1121,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>只有那么些，仅此而已</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1142,12 +1138,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1159,16 +1155,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>それだけ</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>只有那么些，仅此而已</t>
+          <t>弄丢，失去</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>とれる</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>真剣さ</t>
+          <t>生産的</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>认真，严肃（的程度）</t>
+          <t>有生产性的，有成果的</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>しんけんさ</t>
+          <t>せいさんてき</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1197,19 +1197,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜方がいい</t>
+          <t>必ずしも〜ない</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>最好…</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>〜ほうがいい</t>
-        </is>
-      </c>
+          <t>未必，不一定</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1218,15 +1214,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>だいぶ</t>
+          <t>〜方がいい</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>相当；颇；很；很多</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>最好…</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>〜ほうがいい</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.875" customWidth="1" min="2" max="2"/>
@@ -462,10 +462,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -479,10 +484,15 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -496,6 +506,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -517,6 +532,11 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -534,6 +554,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -551,10 +576,15 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -572,10 +602,15 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -589,10 +624,15 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -606,6 +646,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -623,6 +668,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -640,6 +690,11 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -657,6 +712,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -674,6 +734,11 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -695,6 +760,11 @@
           <t>まったく-&gt;完全地</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -712,10 +782,15 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -733,10 +808,15 @@
           <t>振替</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -754,6 +834,11 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -771,6 +856,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -788,6 +878,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -809,6 +904,11 @@
           <t>たがる-&gt;第三人称想要</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -826,6 +926,11 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -847,6 +952,11 @@
           <t>ゆっくり-&gt;慢慢地；不慌不忙地</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -864,6 +974,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -881,6 +996,11 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -898,6 +1018,11 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -919,6 +1044,11 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -936,6 +1066,11 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -953,6 +1088,11 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -970,6 +1110,11 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -987,6 +1132,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1004,6 +1154,11 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1021,6 +1176,11 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1038,6 +1198,11 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1059,6 +1224,11 @@
           <t>ほかり-&gt;除…之外</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1076,10 +1246,15 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1093,6 +1268,11 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1114,6 +1294,11 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1131,6 +1316,11 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1148,6 +1338,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1169,6 +1364,11 @@
           <t>とれる</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1190,6 +1390,11 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1207,6 +1412,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1228,6 +1438,11 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/READING/2_22_12.xlsx
+++ b/READING/2_22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C80ABB-01F4-4FD8-A32A-F9F2F1B7E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF6083A-F533-4A89-99C1-0163501E30A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19215" yWindow="1005" windowWidth="19185" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="203">
   <si>
     <t>Fre</t>
   </si>
@@ -132,9 +132,6 @@
     <t>一点也（不）......</t>
   </si>
   <si>
-    <t>まったく-&gt;完全地</t>
-  </si>
-  <si>
     <t>先</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
   </si>
   <si>
     <t>相当，很</t>
-  </si>
-  <si>
-    <t>ほかり-&gt;除…之外</t>
   </si>
   <si>
     <t>それぞれ</t>
@@ -742,6 +736,22 @@
   </si>
   <si>
     <t>～之后</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まったく-&gt;完全地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほかり-&gt;除…之外</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほかり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除…之外</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1120,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="25.875" customWidth="1"/>
@@ -1334,7 +1344,7 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -1345,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -1359,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -1376,13 +1386,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1393,10 +1403,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -1407,10 +1417,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -1421,13 +1431,13 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>50</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
@@ -1438,10 +1448,10 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
         <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -1452,13 +1462,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>55</v>
-      </c>
-      <c r="E22" t="s">
-        <v>56</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -1469,10 +1479,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -1483,10 +1493,10 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
         <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
@@ -1497,10 +1507,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -1511,13 +1521,13 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
         <v>63</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>65</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -1528,10 +1538,10 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" t="s">
         <v>66</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
@@ -1542,10 +1552,10 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
         <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -1556,10 +1566,10 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
         <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>71</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
@@ -1570,10 +1580,10 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
         <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -1584,10 +1594,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -1598,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
         <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
@@ -1612,10 +1622,10 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
         <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>79</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -1626,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -1643,10 +1653,10 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -1657,10 +1667,10 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -1671,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
         <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>89</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -1688,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -1702,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
@@ -1716,13 +1726,13 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" t="s">
         <v>94</v>
-      </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" t="s">
-        <v>96</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -1733,13 +1743,13 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
         <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>99</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -1750,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -1764,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" t="s">
         <v>102</v>
-      </c>
-      <c r="C43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" t="s">
-        <v>104</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -1781,10 +1791,10 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1792,10 +1802,10 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1803,13 +1813,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
         <v>109</v>
       </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1817,13 +1827,13 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1831,13 +1841,13 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
         <v>115</v>
       </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
       <c r="D48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -1845,10 +1855,10 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -1856,10 +1866,10 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1867,13 +1877,13 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" t="s">
         <v>122</v>
-      </c>
-      <c r="C51" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -1881,10 +1891,10 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -1892,13 +1902,13 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" t="s">
         <v>127</v>
       </c>
-      <c r="C53" t="s">
-        <v>129</v>
-      </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -1906,13 +1916,13 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" t="s">
         <v>130</v>
-      </c>
-      <c r="C54" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
@@ -1920,13 +1930,13 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
         <v>133</v>
       </c>
-      <c r="C55" t="s">
-        <v>135</v>
-      </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
@@ -1934,13 +1944,13 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" t="s">
         <v>136</v>
       </c>
-      <c r="C56" t="s">
-        <v>138</v>
-      </c>
       <c r="D56" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
@@ -1948,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
@@ -1959,10 +1969,10 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -1970,10 +1980,10 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
@@ -1981,10 +1991,10 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -1992,10 +2002,10 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
@@ -2003,10 +2013,10 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
@@ -2014,10 +2024,10 @@
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
@@ -2025,10 +2035,10 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
@@ -2036,13 +2046,13 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" t="s">
         <v>155</v>
       </c>
-      <c r="C65" t="s">
-        <v>157</v>
-      </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
@@ -2050,13 +2060,13 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" t="s">
         <v>158</v>
       </c>
-      <c r="C66" t="s">
-        <v>160</v>
-      </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
@@ -2064,10 +2074,10 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
@@ -2075,13 +2085,13 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" t="s">
         <v>163</v>
-      </c>
-      <c r="C68" t="s">
-        <v>164</v>
-      </c>
-      <c r="D68" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
@@ -2089,10 +2099,10 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
@@ -2100,13 +2110,13 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" t="s">
+        <v>167</v>
+      </c>
+      <c r="D70" t="s">
         <v>168</v>
-      </c>
-      <c r="C70" t="s">
-        <v>169</v>
-      </c>
-      <c r="D70" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
@@ -2114,13 +2124,13 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" t="s">
         <v>171</v>
       </c>
-      <c r="C71" t="s">
-        <v>173</v>
-      </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
@@ -2128,10 +2138,10 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C72" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
@@ -2139,10 +2149,10 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
@@ -2150,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C74" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
@@ -2161,10 +2171,10 @@
         <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
@@ -2172,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" t="s">
         <v>182</v>
-      </c>
-      <c r="C76" t="s">
-        <v>183</v>
-      </c>
-      <c r="D76" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
@@ -2186,10 +2196,10 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -2197,10 +2207,10 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C78" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
@@ -2208,10 +2218,10 @@
         <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
@@ -2219,13 +2229,13 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" t="s">
         <v>191</v>
-      </c>
-      <c r="C80" t="s">
-        <v>192</v>
-      </c>
-      <c r="D80" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
@@ -2233,10 +2243,10 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
@@ -2244,13 +2254,13 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
+        <v>194</v>
+      </c>
+      <c r="C82" t="s">
         <v>196</v>
       </c>
-      <c r="C82" t="s">
-        <v>198</v>
-      </c>
       <c r="D82" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
@@ -2258,10 +2268,18 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C83" t="s">
-        <v>200</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B84" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
